--- a/data/total.xlsx
+++ b/data/total.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fast Computer\OneDrive\Desktop\New folder (15)\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74b89d8f5a3cedb0/Desktop/folder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98E05D2-FEA0-4B50-95E4-F6E6A48B8684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{C98E05D2-FEA0-4B50-95E4-F6E6A48B8684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFED130A-DC82-44FD-8323-340FE9D375AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="63">
   <si>
     <t>Class</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>Tehfeez-ul-Quran</t>
+  </si>
+  <si>
+    <t>K.G-II</t>
   </si>
 </sst>
 </file>
@@ -788,12 +791,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DA98"/>
+  <dimension ref="A1:DA99"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6640625" style="24" customWidth="1"/>
     <col min="10" max="10" width="20.6640625" customWidth="1"/>
     <col min="16" max="16" width="20.58203125" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" customWidth="1"/>
     <col min="40" max="40" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
@@ -1072,17 +1076,17 @@
       <c r="AY3" s="3"/>
       <c r="AZ3" s="3"/>
     </row>
-    <row r="4" spans="1:105" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="4">
+    <row r="4" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="9">
         <v>50</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="9">
         <v>50</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="9">
         <v>50</v>
       </c>
       <c r="E4" s="3"/>
@@ -1094,7 +1098,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="4">
+      <c r="L4" s="9">
         <v>10</v>
       </c>
       <c r="M4" s="3"/>
@@ -1104,16 +1108,16 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="4">
+      <c r="T4" s="9">
         <v>25</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="9">
         <v>25</v>
       </c>
-      <c r="V4" s="4">
+      <c r="V4" s="9">
         <v>25</v>
       </c>
-      <c r="W4" s="4">
+      <c r="W4" s="9">
         <v>20</v>
       </c>
       <c r="X4" s="3"/>
@@ -1146,34 +1150,30 @@
       <c r="AY4" s="3"/>
       <c r="AZ4" s="3"/>
     </row>
-    <row r="5" spans="1:105" s="19" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="28">
-        <v>1</v>
-      </c>
-      <c r="B5" s="19">
-        <v>60</v>
-      </c>
-      <c r="C5" s="19">
-        <v>60</v>
-      </c>
-      <c r="D5" s="19">
-        <v>60</v>
+    <row r="5" spans="1:105" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="4">
+        <v>50</v>
+      </c>
+      <c r="C5" s="4">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4">
+        <v>50</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="19">
-        <v>60</v>
+      <c r="F5" s="20">
+        <v>20</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="19">
-        <v>60</v>
-      </c>
-      <c r="J5" s="19">
-        <v>60</v>
-      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="19">
-        <v>40</v>
+      <c r="L5" s="4">
+        <v>10</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -1182,10 +1182,18 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="T5" s="4">
+        <v>25</v>
+      </c>
+      <c r="U5" s="4">
+        <v>25</v>
+      </c>
+      <c r="V5" s="4">
+        <v>25</v>
+      </c>
+      <c r="W5" s="4">
+        <v>20</v>
+      </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
@@ -1208,35 +1216,42 @@
       <c r="AQ5" s="3"/>
       <c r="AR5" s="3"/>
       <c r="AS5" s="3"/>
-    </row>
-    <row r="6" spans="1:105" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5">
-        <v>70</v>
-      </c>
-      <c r="C6" s="5">
-        <v>70</v>
-      </c>
-      <c r="D6" s="5">
-        <v>70</v>
+      <c r="AT5" s="3"/>
+      <c r="AU5" s="3"/>
+      <c r="AV5" s="3"/>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+      <c r="AZ5" s="3"/>
+    </row>
+    <row r="6" spans="1:105" s="19" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="28">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19">
+        <v>60</v>
+      </c>
+      <c r="C6" s="19">
+        <v>60</v>
+      </c>
+      <c r="D6" s="19">
+        <v>60</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="5">
-        <v>70</v>
+      <c r="F6" s="19">
+        <v>60</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="5">
-        <v>70</v>
-      </c>
-      <c r="J6" s="5">
-        <v>70</v>
+      <c r="I6" s="19">
+        <v>60</v>
+      </c>
+      <c r="J6" s="19">
+        <v>60</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="5">
-        <v>30</v>
+      <c r="L6" s="19">
+        <v>40</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -1272,33 +1287,33 @@
       <c r="AR6" s="3"/>
       <c r="AS6" s="3"/>
     </row>
-    <row r="7" spans="1:105" s="6" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6">
+    <row r="7" spans="1:105" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="29">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5">
         <v>70</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>70</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>70</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>70</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>70</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>70</v>
       </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>30</v>
       </c>
       <c r="M7" s="3"/>
@@ -1335,36 +1350,34 @@
       <c r="AR7" s="3"/>
       <c r="AS7" s="3"/>
     </row>
-    <row r="8" spans="1:105" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="31">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7">
-        <v>100</v>
-      </c>
-      <c r="C8" s="7">
-        <v>100</v>
-      </c>
-      <c r="D8" s="7">
-        <v>100</v>
+    <row r="8" spans="1:105" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="30">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>70</v>
+      </c>
+      <c r="C8" s="6">
+        <v>70</v>
+      </c>
+      <c r="D8" s="6">
+        <v>70</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="7">
-        <v>100</v>
-      </c>
+      <c r="F8" s="6">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="7">
-        <v>100</v>
-      </c>
-      <c r="J8" s="7">
-        <v>100</v>
-      </c>
-      <c r="K8" s="7">
-        <v>100</v>
-      </c>
-      <c r="L8" s="7">
-        <v>50</v>
+      <c r="I8" s="6">
+        <v>70</v>
+      </c>
+      <c r="J8" s="6">
+        <v>70</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="6">
+        <v>30</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -1393,36 +1406,42 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
-      <c r="AN8" s="8"/>
-    </row>
-    <row r="9" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="26">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9">
+      <c r="AN8" s="21"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+    </row>
+    <row r="9" spans="1:105" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="31">
+        <v>4</v>
+      </c>
+      <c r="B9" s="7">
         <v>100</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>100</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>100</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="9">
+      <c r="G9" s="7">
         <v>100</v>
       </c>
-      <c r="I9" s="9">
+      <c r="H9" s="3"/>
+      <c r="I9" s="7">
         <v>100</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="7">
         <v>100</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="7">
         <v>100</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="7">
         <v>50</v>
       </c>
       <c r="M9" s="3"/>
@@ -1452,87 +1471,39 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
-      <c r="AN9" s="21"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="3"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
-      <c r="AS9" s="3"/>
-      <c r="AT9" s="3"/>
-      <c r="AU9" s="3"/>
-      <c r="AV9" s="3"/>
-      <c r="AW9" s="3"/>
-      <c r="AX9" s="3"/>
-      <c r="AY9" s="3"/>
-      <c r="AZ9" s="3"/>
-      <c r="BA9" s="3"/>
-      <c r="BB9" s="3"/>
-      <c r="BC9" s="3"/>
-      <c r="BD9" s="3"/>
-      <c r="BE9" s="3"/>
-      <c r="BF9" s="3"/>
-      <c r="BG9" s="3"/>
-      <c r="BH9" s="3"/>
-      <c r="BI9" s="3"/>
-      <c r="BJ9" s="3"/>
-      <c r="BK9" s="3"/>
-      <c r="BL9" s="3"/>
-      <c r="BM9" s="3"/>
-      <c r="BN9" s="3"/>
-      <c r="BO9" s="3"/>
-      <c r="BP9" s="3"/>
-      <c r="BQ9" s="3"/>
-      <c r="BR9" s="3"/>
-      <c r="BS9" s="3"/>
-      <c r="BT9" s="3"/>
-      <c r="BU9" s="3"/>
-      <c r="BV9" s="3"/>
-      <c r="BW9" s="3"/>
-      <c r="BX9" s="3"/>
-      <c r="BY9" s="3"/>
-      <c r="BZ9" s="3"/>
-      <c r="CA9" s="3"/>
-      <c r="CB9" s="3"/>
-      <c r="CC9" s="3"/>
-      <c r="CD9" s="3"/>
-      <c r="CE9" s="3"/>
-      <c r="CF9" s="3"/>
-      <c r="CG9" s="3"/>
-      <c r="CH9" s="3"/>
-      <c r="CI9" s="3"/>
-      <c r="CJ9" s="3"/>
-      <c r="CK9" s="3"/>
-      <c r="CL9" s="3"/>
-    </row>
-    <row r="10" spans="1:105" x14ac:dyDescent="0.35">
-      <c r="A10" s="32">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>75</v>
-      </c>
-      <c r="C10" s="2">
-        <v>75</v>
-      </c>
-      <c r="D10" s="2">
-        <v>75</v>
-      </c>
-      <c r="E10" s="2">
-        <v>75</v>
-      </c>
-      <c r="G10" s="2">
-        <v>75</v>
-      </c>
-      <c r="I10" s="2">
-        <v>75</v>
-      </c>
-      <c r="J10" s="2">
-        <v>75</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="2">
+      <c r="AN9" s="8"/>
+    </row>
+    <row r="10" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9">
+        <v>100</v>
+      </c>
+      <c r="C10" s="9">
+        <v>100</v>
+      </c>
+      <c r="D10" s="9">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="9">
+        <v>100</v>
+      </c>
+      <c r="I10" s="9">
+        <v>100</v>
+      </c>
+      <c r="J10" s="9">
+        <v>100</v>
+      </c>
+      <c r="K10" s="9">
+        <v>100</v>
+      </c>
+      <c r="L10" s="9">
         <v>50</v>
       </c>
+      <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1611,38 +1582,35 @@
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
     </row>
-    <row r="11" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33">
-        <v>7</v>
-      </c>
-      <c r="B11" s="10">
+    <row r="11" spans="1:105" x14ac:dyDescent="0.35">
+      <c r="A11" s="32">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2">
         <v>75</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="2">
         <v>75</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="2">
         <v>75</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="2">
         <v>75</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="10">
+      <c r="G11" s="2">
         <v>75</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="10">
+      <c r="I11" s="2">
         <v>75</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="2">
         <v>75</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="10">
+      <c r="L11" s="2">
         <v>50</v>
       </c>
-      <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1721,44 +1689,44 @@
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
     </row>
-    <row r="12" spans="1:105" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="11">
+    <row r="12" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="33">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10">
         <v>75</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <v>75</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>75</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="10">
+        <v>75</v>
+      </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="11">
-        <v>65</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="G12" s="10">
+        <v>75</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="10">
+        <v>75</v>
+      </c>
+      <c r="J12" s="10">
+        <v>75</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="10">
         <v>50</v>
       </c>
-      <c r="I12" s="11">
-        <v>50</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="P12" s="11">
-        <v>75</v>
-      </c>
+      <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="11">
-        <v>50</v>
-      </c>
+      <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -1831,20 +1799,44 @@
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
     </row>
-    <row r="13" spans="1:105" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="35" t="s">
-        <v>59</v>
+    <row r="13" spans="1:105" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="11">
+        <v>75</v>
+      </c>
+      <c r="C13" s="11">
+        <v>75</v>
+      </c>
+      <c r="D13" s="11">
+        <v>75</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
+      <c r="G13" s="11">
+        <v>65</v>
+      </c>
+      <c r="H13" s="11">
+        <v>50</v>
+      </c>
+      <c r="I13" s="11">
+        <v>50</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
+      <c r="P13" s="11">
+        <v>75</v>
+      </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
+      <c r="S13" s="11">
+        <v>50</v>
+      </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -1917,9 +1909,9 @@
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
     </row>
-    <row r="14" spans="1:105" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="36" t="s">
-        <v>60</v>
+    <row r="14" spans="1:105" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="35" t="s">
+        <v>59</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2003,43 +1995,20 @@
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
     </row>
-    <row r="15" spans="1:105" s="14" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14">
-        <v>75</v>
-      </c>
-      <c r="C15" s="14">
-        <v>75</v>
-      </c>
-      <c r="D15" s="14">
-        <v>75</v>
+    <row r="15" spans="1:105" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="36" t="s">
+        <v>60</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="14">
-        <v>50</v>
-      </c>
-      <c r="J15" s="14">
-        <v>55</v>
-      </c>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="14">
-        <v>65</v>
-      </c>
-      <c r="O15" s="14">
-        <v>65</v>
-      </c>
-      <c r="P15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="S15" s="14">
-        <v>50</v>
-      </c>
+      <c r="R15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -2112,259 +2081,266 @@
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
     </row>
-    <row r="16" spans="1:105" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="38">
+    <row r="16" spans="1:105" s="14" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="37">
+        <v>8</v>
+      </c>
+      <c r="B16" s="14">
+        <v>75</v>
+      </c>
+      <c r="C16" s="14">
+        <v>75</v>
+      </c>
+      <c r="D16" s="14">
+        <v>75</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="14">
+        <v>50</v>
+      </c>
+      <c r="J16" s="14">
+        <v>55</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="14">
+        <v>65</v>
+      </c>
+      <c r="O16" s="14">
+        <v>65</v>
+      </c>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="S16" s="14">
+        <v>50</v>
+      </c>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="21"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="3"/>
+      <c r="AT16" s="3"/>
+      <c r="AU16" s="3"/>
+      <c r="AV16" s="3"/>
+      <c r="AW16" s="3"/>
+      <c r="AX16" s="3"/>
+      <c r="AY16" s="3"/>
+      <c r="AZ16" s="3"/>
+      <c r="BA16" s="3"/>
+      <c r="BB16" s="3"/>
+      <c r="BC16" s="3"/>
+      <c r="BD16" s="3"/>
+      <c r="BE16" s="3"/>
+      <c r="BF16" s="3"/>
+      <c r="BG16" s="3"/>
+      <c r="BH16" s="3"/>
+      <c r="BI16" s="3"/>
+      <c r="BJ16" s="3"/>
+      <c r="BK16" s="3"/>
+      <c r="BL16" s="3"/>
+      <c r="BM16" s="3"/>
+      <c r="BN16" s="3"/>
+      <c r="BO16" s="3"/>
+      <c r="BP16" s="3"/>
+      <c r="BQ16" s="3"/>
+      <c r="BR16" s="3"/>
+      <c r="BS16" s="3"/>
+      <c r="BT16" s="3"/>
+      <c r="BU16" s="3"/>
+      <c r="BV16" s="3"/>
+      <c r="BW16" s="3"/>
+      <c r="BX16" s="3"/>
+      <c r="BY16" s="3"/>
+      <c r="BZ16" s="3"/>
+      <c r="CA16" s="3"/>
+      <c r="CB16" s="3"/>
+      <c r="CC16" s="3"/>
+      <c r="CD16" s="3"/>
+      <c r="CE16" s="3"/>
+      <c r="CF16" s="3"/>
+      <c r="CG16" s="3"/>
+      <c r="CH16" s="3"/>
+      <c r="CI16" s="3"/>
+      <c r="CJ16" s="3"/>
+      <c r="CK16" s="3"/>
+      <c r="CL16" s="3"/>
+    </row>
+    <row r="17" spans="1:90" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="38">
         <v>9</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B17" s="15">
         <v>75</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C17" s="15">
         <v>75</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D17" s="15">
         <v>75</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="15">
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="15">
         <v>50</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J17" s="15">
         <v>55</v>
       </c>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="15">
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="15">
         <v>65</v>
       </c>
-      <c r="O16" s="15">
+      <c r="O17" s="15">
         <v>65</v>
       </c>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="S16" s="15">
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="S17" s="15">
         <v>50</v>
       </c>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="22"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="22"/>
-      <c r="AF16" s="22"/>
-      <c r="AG16" s="22"/>
-      <c r="AH16" s="22"/>
-      <c r="AI16" s="22"/>
-      <c r="AJ16" s="22"/>
-      <c r="AK16" s="22"/>
-      <c r="AL16" s="22"/>
-      <c r="AM16" s="22"/>
-      <c r="AN16" s="23"/>
-      <c r="AO16" s="22"/>
-      <c r="AP16" s="22"/>
-      <c r="AQ16" s="22"/>
-      <c r="AR16" s="22"/>
-      <c r="AS16" s="22"/>
-      <c r="AT16" s="22"/>
-      <c r="AU16" s="22"/>
-      <c r="AV16" s="22"/>
-      <c r="AW16" s="22"/>
-      <c r="AX16" s="22"/>
-      <c r="AY16" s="22"/>
-      <c r="AZ16" s="22"/>
-      <c r="BA16" s="22"/>
-      <c r="BB16" s="22"/>
-      <c r="BC16" s="22"/>
-      <c r="BD16" s="22"/>
-      <c r="BE16" s="22"/>
-      <c r="BF16" s="22"/>
-      <c r="BG16" s="22"/>
-      <c r="BH16" s="22"/>
-      <c r="BI16" s="22"/>
-      <c r="BJ16" s="22"/>
-      <c r="BK16" s="22"/>
-      <c r="BL16" s="22"/>
-      <c r="BM16" s="22"/>
-      <c r="BN16" s="22"/>
-      <c r="BO16" s="22"/>
-      <c r="BP16" s="22"/>
-      <c r="BQ16" s="22"/>
-      <c r="BR16" s="22"/>
-      <c r="BS16" s="22"/>
-      <c r="BT16" s="22"/>
-      <c r="BU16" s="22"/>
-      <c r="BV16" s="22"/>
-      <c r="BW16" s="22"/>
-      <c r="BX16" s="22"/>
-      <c r="BY16" s="22"/>
-      <c r="BZ16" s="22"/>
-      <c r="CA16" s="22"/>
-      <c r="CB16" s="22"/>
-      <c r="CC16" s="22"/>
-      <c r="CD16" s="22"/>
-      <c r="CE16" s="22"/>
-      <c r="CF16" s="22"/>
-      <c r="CG16" s="22"/>
-      <c r="CH16" s="22"/>
-      <c r="CI16" s="22"/>
-      <c r="CJ16" s="22"/>
-      <c r="CK16" s="22"/>
-      <c r="CL16" s="22"/>
-    </row>
-    <row r="17" spans="1:90" s="16" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="39">
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="22"/>
+      <c r="AF17" s="22"/>
+      <c r="AG17" s="22"/>
+      <c r="AH17" s="22"/>
+      <c r="AI17" s="22"/>
+      <c r="AJ17" s="22"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="22"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="23"/>
+      <c r="AO17" s="22"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="22"/>
+      <c r="AR17" s="22"/>
+      <c r="AS17" s="22"/>
+      <c r="AT17" s="22"/>
+      <c r="AU17" s="22"/>
+      <c r="AV17" s="22"/>
+      <c r="AW17" s="22"/>
+      <c r="AX17" s="22"/>
+      <c r="AY17" s="22"/>
+      <c r="AZ17" s="22"/>
+      <c r="BA17" s="22"/>
+      <c r="BB17" s="22"/>
+      <c r="BC17" s="22"/>
+      <c r="BD17" s="22"/>
+      <c r="BE17" s="22"/>
+      <c r="BF17" s="22"/>
+      <c r="BG17" s="22"/>
+      <c r="BH17" s="22"/>
+      <c r="BI17" s="22"/>
+      <c r="BJ17" s="22"/>
+      <c r="BK17" s="22"/>
+      <c r="BL17" s="22"/>
+      <c r="BM17" s="22"/>
+      <c r="BN17" s="22"/>
+      <c r="BO17" s="22"/>
+      <c r="BP17" s="22"/>
+      <c r="BQ17" s="22"/>
+      <c r="BR17" s="22"/>
+      <c r="BS17" s="22"/>
+      <c r="BT17" s="22"/>
+      <c r="BU17" s="22"/>
+      <c r="BV17" s="22"/>
+      <c r="BW17" s="22"/>
+      <c r="BX17" s="22"/>
+      <c r="BY17" s="22"/>
+      <c r="BZ17" s="22"/>
+      <c r="CA17" s="22"/>
+      <c r="CB17" s="22"/>
+      <c r="CC17" s="22"/>
+      <c r="CD17" s="22"/>
+      <c r="CE17" s="22"/>
+      <c r="CF17" s="22"/>
+      <c r="CG17" s="22"/>
+      <c r="CH17" s="22"/>
+      <c r="CI17" s="22"/>
+      <c r="CJ17" s="22"/>
+      <c r="CK17" s="22"/>
+      <c r="CL17" s="22"/>
+    </row>
+    <row r="18" spans="1:90" s="16" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="39">
         <v>10</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B18" s="16">
         <v>75</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C18" s="16">
         <v>75</v>
       </c>
-      <c r="D17" s="16">
-        <v>75</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="16">
-        <v>50</v>
-      </c>
-      <c r="J17" s="16">
-        <v>55</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="16">
-        <v>65</v>
-      </c>
-      <c r="O17" s="16">
-        <v>65</v>
-      </c>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="S17" s="16">
-        <v>50</v>
-      </c>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="3"/>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
-      <c r="AJ17" s="3"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="3"/>
-      <c r="AN17" s="21"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3"/>
-      <c r="AS17" s="3"/>
-      <c r="AT17" s="3"/>
-      <c r="AU17" s="3"/>
-      <c r="AV17" s="3"/>
-      <c r="AW17" s="3"/>
-      <c r="AX17" s="3"/>
-      <c r="AY17" s="3"/>
-      <c r="AZ17" s="3"/>
-      <c r="BA17" s="3"/>
-      <c r="BB17" s="3"/>
-      <c r="BC17" s="3"/>
-      <c r="BD17" s="3"/>
-      <c r="BE17" s="3"/>
-      <c r="BF17" s="3"/>
-      <c r="BG17" s="3"/>
-      <c r="BH17" s="3"/>
-      <c r="BI17" s="3"/>
-      <c r="BJ17" s="3"/>
-      <c r="BK17" s="3"/>
-      <c r="BL17" s="3"/>
-      <c r="BM17" s="3"/>
-      <c r="BN17" s="3"/>
-      <c r="BO17" s="3"/>
-      <c r="BP17" s="3"/>
-      <c r="BQ17" s="3"/>
-      <c r="BR17" s="3"/>
-      <c r="BS17" s="3"/>
-      <c r="BT17" s="3"/>
-      <c r="BU17" s="3"/>
-      <c r="BV17" s="3"/>
-      <c r="BW17" s="3"/>
-      <c r="BX17" s="3"/>
-      <c r="BY17" s="3"/>
-      <c r="BZ17" s="3"/>
-      <c r="CA17" s="3"/>
-      <c r="CB17" s="3"/>
-      <c r="CC17" s="3"/>
-      <c r="CD17" s="3"/>
-      <c r="CE17" s="3"/>
-      <c r="CF17" s="3"/>
-      <c r="CG17" s="3"/>
-      <c r="CH17" s="3"/>
-      <c r="CI17" s="3"/>
-      <c r="CJ17" s="3"/>
-      <c r="CK17" s="3"/>
-      <c r="CL17" s="3"/>
-    </row>
-    <row r="18" spans="1:90" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="17">
-        <v>75</v>
-      </c>
-      <c r="C18" s="17">
-        <v>75</v>
-      </c>
-      <c r="D18" s="17">
+      <c r="D18" s="16">
         <v>75</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="I18" s="16">
+        <v>50</v>
+      </c>
+      <c r="J18" s="16">
+        <v>55</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="N18" s="16">
+        <v>65</v>
+      </c>
+      <c r="O18" s="16">
+        <v>65</v>
+      </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
+      <c r="S18" s="16">
+        <v>50</v>
+      </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="17">
-        <v>100</v>
-      </c>
+      <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
@@ -2432,44 +2408,41 @@
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
     </row>
-    <row r="19" spans="1:90" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="41">
-        <v>11</v>
-      </c>
-      <c r="B19" s="18">
-        <v>100</v>
-      </c>
-      <c r="C19" s="18">
-        <v>100</v>
-      </c>
-      <c r="D19" s="18">
-        <v>100</v>
+    <row r="19" spans="1:90" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="17">
+        <v>75</v>
+      </c>
+      <c r="C19" s="17">
+        <v>75</v>
+      </c>
+      <c r="D19" s="17">
+        <v>75</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="18">
-        <v>50</v>
-      </c>
-      <c r="J19" s="18">
-        <v>100</v>
-      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-      <c r="Q19" s="18">
-        <v>100</v>
-      </c>
+      <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
+      <c r="X19" s="17">
+        <v>100</v>
+      </c>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
@@ -2537,28 +2510,44 @@
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
     </row>
-    <row r="20" spans="1:90" x14ac:dyDescent="0.35">
-      <c r="A20" s="24">
-        <v>12</v>
-      </c>
-      <c r="B20">
+    <row r="20" spans="1:90" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="41">
+        <v>11</v>
+      </c>
+      <c r="B20" s="18">
         <v>100</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="18">
         <v>100</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="18">
         <v>100</v>
       </c>
-      <c r="J20">
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="18">
+        <v>50</v>
+      </c>
+      <c r="J20" s="18">
         <v>100</v>
       </c>
-      <c r="Q20">
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="18">
         <v>100</v>
       </c>
-      <c r="R20">
-        <v>50</v>
-      </c>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
@@ -2627,6 +2616,27 @@
       <c r="CL20" s="3"/>
     </row>
     <row r="21" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A21" s="24">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>50</v>
+      </c>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
@@ -3034,365 +3044,433 @@
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B56">
-        <v>26</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>37</v>
-      </c>
-      <c r="E56">
-        <v>29</v>
-      </c>
-      <c r="G56">
-        <v>42</v>
-      </c>
-      <c r="I56">
-        <v>24</v>
-      </c>
-      <c r="J56">
-        <v>41</v>
-      </c>
-      <c r="L56">
-        <v>20</v>
-      </c>
+    <row r="27" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="3"/>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="3"/>
+      <c r="AM27" s="3"/>
+      <c r="AN27" s="21"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="3"/>
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="3"/>
+      <c r="AT27" s="3"/>
+      <c r="AU27" s="3"/>
+      <c r="AV27" s="3"/>
+      <c r="AW27" s="3"/>
+      <c r="AX27" s="3"/>
+      <c r="AY27" s="3"/>
+      <c r="AZ27" s="3"/>
+      <c r="BA27" s="3"/>
+      <c r="BB27" s="3"/>
+      <c r="BC27" s="3"/>
+      <c r="BD27" s="3"/>
+      <c r="BE27" s="3"/>
+      <c r="BF27" s="3"/>
+      <c r="BG27" s="3"/>
+      <c r="BH27" s="3"/>
+      <c r="BI27" s="3"/>
+      <c r="BJ27" s="3"/>
+      <c r="BK27" s="3"/>
+      <c r="BL27" s="3"/>
+      <c r="BM27" s="3"/>
+      <c r="BN27" s="3"/>
+      <c r="BO27" s="3"/>
+      <c r="BP27" s="3"/>
+      <c r="BQ27" s="3"/>
+      <c r="BR27" s="3"/>
+      <c r="BS27" s="3"/>
+      <c r="BT27" s="3"/>
+      <c r="BU27" s="3"/>
+      <c r="BV27" s="3"/>
+      <c r="BW27" s="3"/>
+      <c r="BX27" s="3"/>
+      <c r="BY27" s="3"/>
+      <c r="BZ27" s="3"/>
+      <c r="CA27" s="3"/>
+      <c r="CB27" s="3"/>
+      <c r="CC27" s="3"/>
+      <c r="CD27" s="3"/>
+      <c r="CE27" s="3"/>
+      <c r="CF27" s="3"/>
+      <c r="CG27" s="3"/>
+      <c r="CH27" s="3"/>
+      <c r="CI27" s="3"/>
+      <c r="CJ27" s="3"/>
+      <c r="CK27" s="3"/>
+      <c r="CL27" s="3"/>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B57">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C57">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E57">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G57">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I57">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J57">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L57">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B58">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C58">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D58">
-        <v>45.5</v>
+        <v>36</v>
       </c>
       <c r="E58">
-        <v>36.5</v>
+        <v>48</v>
       </c>
       <c r="G58">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="I58">
-        <v>28.5</v>
+        <v>26</v>
       </c>
       <c r="J58">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L58">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B59">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D59">
-        <v>27</v>
+        <v>45.5</v>
       </c>
       <c r="E59">
-        <v>25</v>
+        <v>36.5</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>46.5</v>
       </c>
       <c r="I59">
-        <v>13</v>
+        <v>28.5</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="L59">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B60">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>27</v>
+      </c>
+      <c r="E60">
+        <v>25</v>
+      </c>
+      <c r="G60">
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>13</v>
+      </c>
+      <c r="J60">
         <v>4</v>
       </c>
-      <c r="D60">
-        <v>4</v>
-      </c>
-      <c r="E60">
-        <v>20</v>
-      </c>
-      <c r="G60">
-        <v>47</v>
-      </c>
-      <c r="I60">
-        <v>25</v>
-      </c>
-      <c r="J60">
+      <c r="L60">
         <v>30</v>
-      </c>
-      <c r="L60">
-        <v>40</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B61">
+        <v>28</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
+        <v>20</v>
+      </c>
+      <c r="G61">
+        <v>47</v>
+      </c>
+      <c r="I61">
+        <v>25</v>
+      </c>
+      <c r="J61">
+        <v>30</v>
+      </c>
+      <c r="L61">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B62">
         <v>43.5</v>
       </c>
-      <c r="C61">
+      <c r="C62">
         <v>44</v>
       </c>
-      <c r="D61">
+      <c r="D62">
         <v>48.5</v>
       </c>
-      <c r="E61">
+      <c r="E62">
         <v>47.5</v>
       </c>
-      <c r="G61">
+      <c r="G62">
         <v>48</v>
       </c>
-      <c r="I61">
+      <c r="I62">
         <v>33</v>
       </c>
-      <c r="J61">
+      <c r="J62">
         <v>47.5</v>
       </c>
-      <c r="L61">
+      <c r="L62">
         <v>43</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B67">
-        <v>12</v>
-      </c>
-      <c r="C67">
-        <v>28</v>
-      </c>
-      <c r="D67">
-        <v>43</v>
-      </c>
-      <c r="E67">
-        <v>22</v>
-      </c>
-      <c r="G67">
-        <v>30</v>
-      </c>
-      <c r="I67">
-        <v>44</v>
-      </c>
-      <c r="J67">
-        <v>45</v>
-      </c>
-      <c r="L67">
-        <v>40</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B68">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C68">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D68">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E68">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G68">
+        <v>30</v>
+      </c>
+      <c r="I68">
         <v>44</v>
       </c>
-      <c r="I68">
-        <v>49</v>
-      </c>
       <c r="J68">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L68">
         <v>40</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B69">
+        <v>29</v>
+      </c>
       <c r="C69">
+        <v>25</v>
+      </c>
+      <c r="D69">
+        <v>53</v>
+      </c>
+      <c r="E69">
+        <v>43</v>
+      </c>
+      <c r="G69">
+        <v>44</v>
+      </c>
+      <c r="I69">
+        <v>49</v>
+      </c>
+      <c r="J69">
+        <v>49</v>
+      </c>
+      <c r="L69">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C70">
         <v>45.5</v>
       </c>
-      <c r="D69">
+      <c r="D70">
         <v>37</v>
       </c>
-      <c r="E69">
+      <c r="E70">
         <v>32.5</v>
       </c>
-      <c r="G69">
+      <c r="G70">
         <v>48</v>
       </c>
-      <c r="I69">
+      <c r="I70">
         <v>30</v>
       </c>
-      <c r="J69">
+      <c r="J70">
         <v>27</v>
       </c>
-      <c r="L69">
+      <c r="L70">
         <v>45</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B70">
-        <v>26</v>
-      </c>
-      <c r="C70">
-        <v>32</v>
-      </c>
-      <c r="D70">
-        <v>31</v>
-      </c>
-      <c r="E70">
-        <v>33</v>
-      </c>
-      <c r="G70">
-        <v>35</v>
-      </c>
-      <c r="I70">
-        <v>43</v>
-      </c>
-      <c r="J70">
-        <v>46</v>
-      </c>
-      <c r="L70">
-        <v>35</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B71">
+        <v>26</v>
+      </c>
+      <c r="C71">
+        <v>32</v>
+      </c>
+      <c r="D71">
+        <v>31</v>
+      </c>
+      <c r="E71">
+        <v>33</v>
+      </c>
+      <c r="G71">
+        <v>35</v>
+      </c>
+      <c r="I71">
+        <v>43</v>
+      </c>
+      <c r="J71">
+        <v>46</v>
+      </c>
+      <c r="L71">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B72">
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B97" t="s">
+    <row r="98" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B98" t="s">
         <v>28</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C98" t="s">
         <v>28</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D98" t="s">
         <v>28</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E98" t="s">
         <v>27</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F98" t="s">
         <v>27</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G98" t="s">
         <v>28</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H98" t="s">
         <v>28</v>
       </c>
-      <c r="I97" t="s">
+      <c r="I98" t="s">
         <v>54</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J98" t="s">
         <v>27</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K98" t="s">
         <v>27</v>
       </c>
-      <c r="L97" t="s">
+      <c r="L98" t="s">
         <v>27</v>
       </c>
-      <c r="M97" t="s">
+      <c r="M98" t="s">
         <v>27</v>
       </c>
-      <c r="N97" t="s">
+      <c r="N98" t="s">
         <v>27</v>
       </c>
-      <c r="O97" t="s">
+      <c r="O98" t="s">
         <v>27</v>
       </c>
-      <c r="P97" t="s">
+      <c r="P98" t="s">
         <v>28</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="Q98" t="s">
         <v>27</v>
       </c>
-      <c r="R97" t="s">
+      <c r="R98" t="s">
         <v>28</v>
       </c>
-      <c r="S97" t="s">
+      <c r="S98" t="s">
         <v>27</v>
       </c>
-      <c r="T97" t="s">
+      <c r="T98" t="s">
         <v>27</v>
       </c>
-      <c r="U97" t="s">
+      <c r="U98" t="s">
         <v>27</v>
       </c>
-      <c r="V97" t="s">
+      <c r="V98" t="s">
         <v>27</v>
       </c>
-      <c r="W97" t="s">
+      <c r="W98" t="s">
         <v>27</v>
       </c>
-      <c r="X97" t="s">
+      <c r="X98" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="2:24" x14ac:dyDescent="0.35">
-      <c r="B98">
+    <row r="99" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B99">
         <v>45</v>
       </c>
-      <c r="C98">
+      <c r="C99">
         <v>23</v>
       </c>
-      <c r="D98">
+      <c r="D99">
         <v>44</v>
       </c>
-      <c r="G98">
+      <c r="G99">
         <v>45</v>
       </c>
-      <c r="H98">
+      <c r="H99">
         <v>35</v>
       </c>
-      <c r="I98">
+      <c r="I99">
         <v>32</v>
       </c>
-      <c r="L98">
+      <c r="L99">
         <v>33</v>
       </c>
-      <c r="P98">
+      <c r="P99">
         <v>33</v>
       </c>
-      <c r="S98">
+      <c r="S99">
         <v>32</v>
       </c>
     </row>

--- a/data/total.xlsx
+++ b/data/total.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74b89d8f5a3cedb0/Desktop/folder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{C98E05D2-FEA0-4B50-95E4-F6E6A48B8684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFED130A-DC82-44FD-8323-340FE9D375AA}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{C98E05D2-FEA0-4B50-95E4-F6E6A48B8684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5AE9225-2D62-4D63-AAD6-722E1E9C60D5}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="74">
   <si>
     <t>Class</t>
   </si>
@@ -206,10 +206,43 @@
     <t>10 (Art Group)</t>
   </si>
   <si>
-    <t>Tehfeez-ul-Quran</t>
-  </si>
-  <si>
     <t>K.G-II</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (1st)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (2nd)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (3rd)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (4th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (5th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (6th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (8th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (9th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (10th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (7th)</t>
+  </si>
+  <si>
+    <t>Tehfeez ul Quran (11th)</t>
   </si>
 </sst>
 </file>
@@ -467,6 +500,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1078,7 +1115,7 @@
     </row>
     <row r="4" spans="1:105" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="9">
         <v>50</v>
@@ -2410,7 +2447,7 @@
     </row>
     <row r="19" spans="1:90" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="17">
         <v>75</v>
@@ -2704,7 +2741,41 @@
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
     </row>
-    <row r="22" spans="1:90" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:90" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="17">
+        <v>75</v>
+      </c>
+      <c r="C22" s="17">
+        <v>75</v>
+      </c>
+      <c r="D22" s="17">
+        <v>75</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="17">
+        <v>100</v>
+      </c>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
@@ -2773,6 +2844,21 @@
       <c r="CL22" s="3"/>
     </row>
     <row r="23" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A23" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="17">
+        <v>75</v>
+      </c>
+      <c r="C23" s="17">
+        <v>75</v>
+      </c>
+      <c r="D23" s="17">
+        <v>75</v>
+      </c>
+      <c r="X23" s="17">
+        <v>100</v>
+      </c>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
@@ -2841,6 +2927,21 @@
       <c r="CL23" s="3"/>
     </row>
     <row r="24" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A24" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="17">
+        <v>75</v>
+      </c>
+      <c r="C24" s="17">
+        <v>75</v>
+      </c>
+      <c r="D24" s="17">
+        <v>75</v>
+      </c>
+      <c r="X24" s="17">
+        <v>100</v>
+      </c>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
@@ -2909,6 +3010,21 @@
       <c r="CL24" s="3"/>
     </row>
     <row r="25" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A25" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="17">
+        <v>75</v>
+      </c>
+      <c r="C25" s="17">
+        <v>75</v>
+      </c>
+      <c r="D25" s="17">
+        <v>75</v>
+      </c>
+      <c r="X25" s="17">
+        <v>100</v>
+      </c>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
@@ -2977,6 +3093,21 @@
       <c r="CL25" s="3"/>
     </row>
     <row r="26" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A26" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="17">
+        <v>75</v>
+      </c>
+      <c r="C26" s="17">
+        <v>75</v>
+      </c>
+      <c r="D26" s="17">
+        <v>75</v>
+      </c>
+      <c r="X26" s="17">
+        <v>100</v>
+      </c>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
@@ -3045,6 +3176,21 @@
       <c r="CL26" s="3"/>
     </row>
     <row r="27" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A27" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="17">
+        <v>75</v>
+      </c>
+      <c r="C27" s="17">
+        <v>75</v>
+      </c>
+      <c r="D27" s="17">
+        <v>75</v>
+      </c>
+      <c r="X27" s="17">
+        <v>100</v>
+      </c>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
@@ -3112,6 +3258,91 @@
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
     </row>
+    <row r="28" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A28" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="17">
+        <v>75</v>
+      </c>
+      <c r="C28" s="17">
+        <v>75</v>
+      </c>
+      <c r="D28" s="17">
+        <v>75</v>
+      </c>
+      <c r="X28" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A29" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="17">
+        <v>75</v>
+      </c>
+      <c r="C29" s="17">
+        <v>75</v>
+      </c>
+      <c r="D29" s="17">
+        <v>75</v>
+      </c>
+      <c r="X29" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A30" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="17">
+        <v>75</v>
+      </c>
+      <c r="C30" s="17">
+        <v>75</v>
+      </c>
+      <c r="D30" s="17">
+        <v>75</v>
+      </c>
+      <c r="X30" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A31" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="17">
+        <v>75</v>
+      </c>
+      <c r="C31" s="17">
+        <v>75</v>
+      </c>
+      <c r="D31" s="17">
+        <v>75</v>
+      </c>
+      <c r="X31" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:90" x14ac:dyDescent="0.35">
+      <c r="A32" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="17">
+        <v>75</v>
+      </c>
+      <c r="C32" s="17">
+        <v>75</v>
+      </c>
+      <c r="D32" s="17">
+        <v>75</v>
+      </c>
+      <c r="X32" s="17">
+        <v>100</v>
+      </c>
+    </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>26</v>
